--- a/data/trans_dic/DCD_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/DCD_R-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,07</t>
+          <t>0,5; 4,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,42; 23,2</t>
+          <t>11,22; 23,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,38; 11,17</t>
+          <t>5,79; 11,56</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,32; 8,82</t>
+          <t>3,46; 8,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 16,97</t>
+          <t>8,22; 17,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,67; 12,01</t>
+          <t>7,11; 12,22</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,92; 12,28</t>
+          <t>6,75; 11,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,41; 19,37</t>
+          <t>12,23; 19,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,8; 14,95</t>
+          <t>10,89; 14,93</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 16,16</t>
+          <t>5,0; 16,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,42; 27,27</t>
+          <t>20,78; 27,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 20,61</t>
+          <t>10,7; 20,91</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,65; 23,84</t>
+          <t>17,76; 24,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,2; 36,04</t>
+          <t>30,16; 36,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,86; 29,19</t>
+          <t>24,75; 29,22</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,4; 23,68</t>
+          <t>17,66; 24,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,35; 36,54</t>
+          <t>10,24; 36,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,44; 29,33</t>
+          <t>12,02; 29,31</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29,03; 37,14</t>
+          <t>28,6; 37,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52,06; 59,0</t>
+          <t>51,6; 59,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43,71; 49,47</t>
+          <t>43,71; 49,1</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,42; 14,94</t>
+          <t>10,55; 15,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,8; 27,7</t>
+          <t>20,58; 27,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,11; 21,21</t>
+          <t>16,92; 21,14</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1979; 20263</t>
+          <t>1992; 19500</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35761; 72660</t>
+          <t>35152; 72502</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38377; 79656</t>
+          <t>41304; 82452</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14076; 37374</t>
+          <t>14672; 37467</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38461; 86898</t>
+          <t>42076; 88033</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62387; 112332</t>
+          <t>66504; 114298</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>37112; 65839</t>
+          <t>36213; 64313</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>73464; 114668</t>
+          <t>72376; 115423</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>121810; 168637</t>
+          <t>122917; 168447</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42181; 143466</t>
+          <t>44387; 144973</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>145546; 194413</t>
+          <t>148112; 195902</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>158898; 329935</t>
+          <t>171288; 334652</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>99080; 133825</t>
+          <t>99651; 136002</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>165480; 197481</t>
+          <t>165245; 198252</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>275784; 323771</t>
+          <t>274485; 324144</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>64052; 87195</t>
+          <t>65023; 88362</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>56879; 222283</t>
+          <t>62311; 222748</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>121455; 286451</t>
+          <t>117425; 286226</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>82073; 105023</t>
+          <t>80879; 105210</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>221690; 251253</t>
+          <t>219724; 251309</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>309738; 350511</t>
+          <t>309740; 347941</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>360611; 516813</t>
+          <t>364903; 519297</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>772295; 1028292</t>
+          <t>764091; 1028185</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1227473; 1521176</t>
+          <t>1213709; 1516243</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DCD_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/DCD_R-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,88</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,22; 23,15</t>
+          <t>11,7; 22,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,79; 11,56</t>
+          <t>6,19; 12,36</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 8,85</t>
+          <t>3,26; 8,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,22; 17,19</t>
+          <t>10,93; 17,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,11; 12,22</t>
+          <t>7,85; 12,17</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,75; 11,99</t>
+          <t>6,18; 10,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,23; 19,5</t>
+          <t>15,9; 21,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,89; 14,93</t>
+          <t>11,73; 15,29</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 16,33</t>
+          <t>12,19; 17,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,78; 27,48</t>
+          <t>22,84; 28,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,7; 20,91</t>
+          <t>18,29; 22,14</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,76; 24,23</t>
+          <t>17,31; 23,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,16; 36,18</t>
+          <t>30,05; 35,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,75; 29,22</t>
+          <t>24,51; 29,1</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,66; 24,0</t>
+          <t>16,87; 23,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,24; 36,61</t>
+          <t>32,7; 39,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,02; 29,31</t>
+          <t>25,91; 30,83</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,65%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,6; 37,21</t>
+          <t>28,37; 37,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>51,6; 59,02</t>
+          <t>52,08; 58,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43,71; 49,1</t>
+          <t>43,72; 49,13</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,55; 15,01</t>
+          <t>12,96; 15,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,58; 27,7</t>
+          <t>26,92; 29,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,92; 21,14</t>
+          <t>20,32; 22,12</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50324</t>
+          <t>60871</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>67799</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1992; 19500</t>
+          <t>0; 19113</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35152; 72502</t>
+          <t>42431; 82765</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41304; 82452</t>
+          <t>47688; 95229</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>22820</t>
+          <t>26175</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>66502</t>
+          <t>71381</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89322</t>
+          <t>97556</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14672; 37467</t>
+          <t>15535; 42237</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42076; 88033</t>
+          <t>54825; 88327</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66504; 114298</t>
+          <t>76824; 119112</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48943</t>
+          <t>52228</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>97317</t>
+          <t>113298</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>146260</t>
+          <t>165525</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36213; 64313</t>
+          <t>38371; 67240</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>72376; 115423</t>
+          <t>99114; 132807</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122917; 168447</t>
+          <t>145937; 190169</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>97825</t>
+          <t>103886</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>173392</t>
+          <t>187024</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>271217</t>
+          <t>290911</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44387; 144973</t>
+          <t>85435; 125041</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>148112; 195902</t>
+          <t>168298; 206546</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>171288; 334652</t>
+          <t>262961; 318333</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>117108</t>
+          <t>123685</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>182259</t>
+          <t>200521</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>299367</t>
+          <t>324206</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>99651; 136002</t>
+          <t>105480; 145150</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>165245; 198252</t>
+          <t>182953; 218975</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>274485; 324144</t>
+          <t>298568; 354449</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>75576</t>
+          <t>81378</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>143235</t>
+          <t>157730</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>218811</t>
+          <t>239108</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>65023; 88362</t>
+          <t>68680; 95729</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>62311; 222748</t>
+          <t>143624; 172982</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>117425; 286226</t>
+          <t>219277; 260887</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>93101</t>
+          <t>102059</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>236516</t>
+          <t>259412</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>329617</t>
+          <t>361471</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>80879; 105210</t>
+          <t>87997; 116596</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>219724; 251309</t>
+          <t>241982; 273990</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>309740; 347941</t>
+          <t>338708; 380644</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>462580</t>
+          <t>496338</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>949546</t>
+          <t>1050237</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1412125</t>
+          <t>1546575</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>364903; 519297</t>
+          <t>457883; 543216</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>764091; 1028185</t>
+          <t>1006147; 1101531</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1213709; 1516243</t>
+          <t>1477371; 1607726</t>
         </is>
       </c>
     </row>
